--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,17 +536,68 @@
           <t>Sent 1 GEMS - None</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ARB-USD:6</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>00:12:16 IST</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sent 1 GEMS - None</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>ARB-USD:6</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -610,10 +661,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -622,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,17 +587,68 @@
           <t>Sent 1 GEMS - None</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ARB-USD:6</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>00:16:22 IST</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sent 1 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>ARB-USD:6</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -661,10 +712,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -673,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,17 +638,68 @@
           <t>Sent 1 GEMS - 200</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ARB-USD:6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>00:33:50 IST</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sent 1 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>ARB-USD:6</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -712,10 +763,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -724,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,17 +689,68 @@
           <t>Sent 1 GEMS - 200</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ARB-USD:6</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>00:52:13 IST</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sent 12 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ARB-USD:6</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -763,10 +814,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -775,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -792,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +966,198 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>00:52:19 IST</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AAVE-USD</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>97.87000274658205</v>
+      </c>
+      <c r="F3" t="n">
+        <v>510</v>
+      </c>
+      <c r="G3" t="n">
+        <v>95.91</v>
+      </c>
+      <c r="H3" t="n">
+        <v>101.78</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Trend Pullback, RSI 63 Score:3 RVOL:1.4x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>00:52:19 IST</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ADA-USD</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1745000034570694</v>
+      </c>
+      <c r="F4" t="n">
+        <v>222222</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Trend Pullback, RSI 60 Score:3 RVOL:0.8x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>00:52:19 IST</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HBAR-USD</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0717300027608871</v>
+      </c>
+      <c r="F5" t="n">
+        <v>578033</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>VWAP Reclaim, RSI 58 Score:2 RVOL:1.6x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>00:52:19 IST</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>65805.859375</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>64489.74</v>
+      </c>
+      <c r="H6" t="n">
+        <v>68438.09</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>RSI 66, EMA Bull Score:2 RVOL:1.1x</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,17 +740,68 @@
           <t>Sent 12 GEMS - 200</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01:01:20 IST</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sent 13 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -814,10 +865,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -826,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -843,7 +894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1095,18 +1146,28 @@
       <c r="H5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>01:01:23 IST</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-2.41</v>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>VWAP Reclaim, RSI 58 Score:2 RVOL:1.6x</t>
+          <t>VWAP Reclaim, RSI 58 Score:2 RVOL:1.6x | Target Hit</t>
         </is>
       </c>
     </row>
@@ -1158,6 +1219,54 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01:01:23 IST</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HBAR-USD</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.07169</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.070256</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.074558</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>VWAP Reclaim, RSI 58 Score:2 RVOL:1.6x</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,17 +791,68 @@
           <t>Sent 13 GEMS - 200</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>01:09:40 IST</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sent 13 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -865,10 +916,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -877,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,17 +842,68 @@
           <t>Sent 13 GEMS - 200</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01:25:56 IST</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>13</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sent 13 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -916,10 +967,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -928,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -945,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,7 +1079,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00:01:28 IST</t>
+          <t>01:26:00 IST</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1042,16 +1093,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0007570616435258999</v>
+        <v>0.00075706</v>
       </c>
       <c r="F2" t="n">
-        <v>1320896</v>
+        <v>5000</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.00074192</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.00078734</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -1064,7 +1115,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>RVOL 20.0x, 20D Break 0&gt;0 Score:6 RVOL:20.0x</t>
+          <t>RVOL 15.0x, 20D Breakout Score:7 RVOL:15.0x</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1127,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>00:52:19 IST</t>
+          <t>01:26:00 IST</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1090,16 +1141,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>97.87000274658205</v>
+        <v>97.84</v>
       </c>
       <c r="F3" t="n">
-        <v>510</v>
+        <v>204</v>
       </c>
       <c r="G3" t="n">
-        <v>95.91</v>
+        <v>95.88</v>
       </c>
       <c r="H3" t="n">
-        <v>101.78</v>
+        <v>101.75</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -1124,7 +1175,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>00:52:19 IST</t>
+          <t>01:26:00 IST</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1138,16 +1189,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1745000034570694</v>
+        <v>0.1744</v>
       </c>
       <c r="F4" t="n">
-        <v>222222</v>
+        <v>10000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.17</v>
+        <v>0.1709</v>
       </c>
       <c r="H4" t="n">
-        <v>0.18</v>
+        <v>0.1814</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -1172,7 +1223,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>00:52:19 IST</t>
+          <t>01:26:00 IST</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1186,39 +1237,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0717300027608871</v>
+        <v>0.07167</v>
       </c>
       <c r="F5" t="n">
-        <v>578033</v>
+        <v>5000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07023699999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>01:01:23 IST</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-2.41</v>
-      </c>
+        <v>0.07453700000000001</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>VWAP Reclaim, RSI 58 Score:2 RVOL:1.6x | Target Hit</t>
+          <t>VWAP Reclaim, RSI 58 Score:2 RVOL:1.6x</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1271,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>00:52:19 IST</t>
+          <t>01:26:00 IST</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1244,16 +1285,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65805.859375</v>
+        <v>65880.89999999999</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>64489.74</v>
+        <v>64563.28</v>
       </c>
       <c r="H6" t="n">
-        <v>68438.09</v>
+        <v>68516.14</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -1270,54 +1311,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>01:01:23 IST</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CRYPTO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HBAR-USD</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.07169</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.070256</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.074558</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>VWAP Reclaim, RSI 58 Score:2 RVOL:1.6x</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -893,17 +893,68 @@
           <t>Sent 13 GEMS - 200</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>02:35:44 IST</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sent 13 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -967,10 +1018,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -979,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,17 +944,68 @@
           <t>Sent 13 GEMS - 200</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>04:31:52 IST</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sent 13 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1018,10 +1069,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1030,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,17 +995,68 @@
           <t>Sent 13 GEMS - 200</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08:06:59 IST</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CRYPTO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sent 12 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1069,10 +1120,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1081,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,17 +1046,68 @@
           <t>Sent 12 GEMS - 200</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10:19:58 IST</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>32</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sent 32 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>ARB-USD:7 | AAVE-USD:3 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BPCL.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | ULTRACEMCO.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1120,22 +1171,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,6 +1515,246 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10:20:10 IST</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BPCL.NS</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>63</v>
+      </c>
+      <c r="G7" t="n">
+        <v>309.58</v>
+      </c>
+      <c r="H7" t="n">
+        <v>328.54</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Trend Pullback, RSI 58 Score:3 RVOL:0.5x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10:20:10 IST</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO.NS</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5170</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5066.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5376.8</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>RSI 71, EMA Bull Score:2 RVOL:0.6x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:20:10 IST</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JSWSTEEL.NS</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1268</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1242.64</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1318.72</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>RSI 65, EMA Bull Score:2 RVOL:0.6x</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10:20:10 IST</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TVSMOTOR.NS</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3946.1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3867.18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4103.94</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>RSI 70, EMA Bull Score:2 RVOL:0.4x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10:20:10 IST</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO.NS</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>11915</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11676.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12391.6</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>RSI 59, EMA Bull Score:2 RVOL:0.4x</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,17 +1097,68 @@
           <t>Sent 32 GEMS - 200</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BPCL.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | ULTRACEMCO.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10:25:52 IST</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sent 34 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>BPCL.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | ULTRACEMCO.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OFSS.NS:3 | BPCL.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1171,22 +1222,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,17 +1148,68 @@
           <t>Sent 34 GEMS - 200</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OFSS.NS:3 | BPCL.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10:30:40 IST</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>26</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>35</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sent 35 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>OFSS.NS:3 | BPCL.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1222,22 +1273,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="C2" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,17 +1199,68 @@
           <t>Sent 35 GEMS - 200</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>OFSS.NS:3 | BPCL.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10:42:09 IST</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>27</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>36</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sent 36 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>OFSS.NS:3 | BPCL.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>OFSS.NS:3 | BPCL.NS:3 | JSWSTEEL.NS:2 | HEROMOTOCO.NS:2 | TVSMOTOR.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1273,22 +1324,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,17 +1250,68 @@
           <t>Sent 36 GEMS - 200</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>OFSS.NS:3 | BPCL.NS:3 | JSWSTEEL.NS:2 | HEROMOTOCO.NS:2 | TVSMOTOR.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11:01:01 IST</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>28</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>37</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sent 37 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>OFSS.NS:3 | BPCL.NS:3 | JSWSTEEL.NS:2 | HEROMOTOCO.NS:2 | TVSMOTOR.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>OFSS.NS:3 | BPCL.NS:3 | BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1324,22 +1375,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="C2" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D2" t="n">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1301,17 +1301,68 @@
           <t>Sent 37 GEMS - 200</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>OFSS.NS:3 | BPCL.NS:3 | BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11:12:46 IST</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>27</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>36</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sent 36 GEMS - 200</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>OFSS.NS:3 | BPCL.NS:3 | BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1375,22 +1426,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,17 +1352,68 @@
           <t>Sent 36 GEMS - 200</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>OFSS.NS:3 | BPCL.NS:3 | BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12:13:11 IST</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>32</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>OFSS.NS:3 | BPCL.NS:3 | BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | ADA-USD:3 | HBAR-USD:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>BPCL.NS:3 | BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2 | XRP-USD:2 | LTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1426,22 +1477,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="C2" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D2" t="n">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1403,17 +1403,68 @@
           <t>Sent</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>BPCL.NS:3 | BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2 | XRP-USD:2 | LTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12:17:54 IST</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>32</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>BPCL.NS:3 | BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | TVSMOTOR.NS:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2 | XRP-USD:2 | LTC-USD:2</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | BPCL.NS:2 | TVSMOTOR.NS:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2 | XRP-USD:2 | LTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1477,22 +1528,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="C2" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D2" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1454,17 +1454,68 @@
           <t>Sent</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | BPCL.NS:2 | TVSMOTOR.NS:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2 | XRP-USD:2 | LTC-USD:2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13:08:30 IST</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>19</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>26</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>BAJAJFINSV.NS:3 | HEROMOTOCO.NS:2 | JSWSTEEL.NS:2 | BPCL.NS:2 | TVSMOTOR.NS:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2 | XRP-USD:2 | LTC-USD:2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO.NS:4 | BAJAJFINSV.NS:3 | JSWSTEEL.NS:2 | ULTRACEMCO.NS:2 | TVSMOTOR.NS:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2 | LTC-USD:2 | XRP-USD:2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1528,22 +1579,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="C2" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D2" t="n">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Logs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All Runs" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Paper Trades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +495,36 @@
           <t>Weekday</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Gems_Found</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>New_Entries</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Closed_Trades</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Open_Positions</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Total_PnL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -547,6 +576,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -598,6 +633,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -649,6 +690,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -700,6 +747,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -751,6 +804,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -802,6 +861,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -853,6 +918,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -904,6 +975,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -955,6 +1032,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1006,6 +1089,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1057,6 +1146,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1108,6 +1203,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1159,6 +1260,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1210,6 +1317,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1261,6 +1374,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1312,6 +1431,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1363,6 +1488,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1414,6 +1545,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1465,6 +1602,12 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1505,11 +1648,7 @@
           <t>Sent</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>HEROMOTOCO.NS:4 | BAJAJFINSV.NS:3 | JSWSTEEL.NS:2 | ULTRACEMCO.NS:2 | TVSMOTOR.NS:2 | BTC-USD:2 | ETH-USD:2 | LINK-USD:2 | LTC-USD:2 | XRP-USD:2</t>
@@ -1520,6 +1659,53 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14:33:26 IST</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1543,32 +1729,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Total_Found</t>
+          <t>Gems_Found</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Filtered_Sent_Count</t>
+          <t>New_Entries</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Indian_Count</t>
+          <t>Closed_Trades</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>US_Count</t>
+          <t>Open_Positions</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Crypto_Count</t>
+          <t>Capital</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Decay_Count</t>
+          <t>Total_PnL</t>
         </is>
       </c>
     </row>
@@ -1578,590 +1764,12 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>393</v>
-      </c>
-      <c r="C2" t="n">
-        <v>87</v>
-      </c>
-      <c r="D2" t="n">
-        <v>225</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>159</v>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Time_IST</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mode</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Entry_Price</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Exit_Price</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Exit_Time</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>P&amp;L</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>P&amp;L_%</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>01:26:00 IST</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CRYPTO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ARB-USD</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.00075706</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.00074192</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.00078734</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>RVOL 15.0x, 20D Breakout Score:7 RVOL:15.0x</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>01:26:00 IST</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CRYPTO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AAVE-USD</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>97.84</v>
-      </c>
-      <c r="F3" t="n">
-        <v>204</v>
-      </c>
-      <c r="G3" t="n">
-        <v>95.88</v>
-      </c>
-      <c r="H3" t="n">
-        <v>101.75</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Trend Pullback, RSI 63 Score:3 RVOL:1.4x</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>01:26:00 IST</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CRYPTO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ADA-USD</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.1744</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.1709</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.1814</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Trend Pullback, RSI 60 Score:3 RVOL:0.8x</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>01:26:00 IST</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CRYPTO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HBAR-USD</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.07167</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.07023699999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.07453700000000001</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>VWAP Reclaim, RSI 58 Score:2 RVOL:1.6x</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>01:26:00 IST</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CRYPTO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>BTC-USD</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>65880.89999999999</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>64563.28</v>
-      </c>
-      <c r="H6" t="n">
-        <v>68516.14</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>RSI 66, EMA Bull Score:2 RVOL:1.1x</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>10:20:10 IST</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>BPCL.NS</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>315.9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>63</v>
-      </c>
-      <c r="G7" t="n">
-        <v>309.58</v>
-      </c>
-      <c r="H7" t="n">
-        <v>328.54</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Trend Pullback, RSI 58 Score:3 RVOL:0.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>10:20:10 IST</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO.NS</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5170</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5066.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5376.8</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>RSI 71, EMA Bull Score:2 RVOL:0.6x</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>10:20:10 IST</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>JSWSTEEL.NS</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1268</v>
-      </c>
-      <c r="F9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1242.64</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1318.72</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>RSI 65, EMA Bull Score:2 RVOL:0.6x</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>10:20:10 IST</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TVSMOTOR.NS</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>3946.1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3867.18</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4103.94</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>RSI 70, EMA Bull Score:2 RVOL:0.4x</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>10:20:10 IST</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ULTRACEMCO.NS</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>11915</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>11676.7</v>
-      </c>
-      <c r="H11" t="n">
-        <v>12391.6</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>RSI 59, EMA Bull Score:2 RVOL:0.4x</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
